--- a/Config/Datas/BuffDatas/BuffDatas.xlsx
+++ b/Config/Datas/BuffDatas/BuffDatas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\BuffDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85528DC9-B8C7-4556-AC9C-CE82A003346D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9308A1-76EE-4645-9DCC-E273DD77BF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -76,6 +76,14 @@
   </si>
   <si>
     <t>纵享丝滑~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effectDescription</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用一张卡牌后，消耗1点丝滑，抽一张卡牌</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -423,14 +431,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="11.25" customWidth="1"/>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="5" max="5" width="11.25" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -441,16 +449,19 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -463,14 +474,17 @@
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>10</v>
       </c>
@@ -478,9 +492,12 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="b">
+      <c r="G3" t="b">
         <v>1</v>
       </c>
     </row>
